--- a/new-info47/web.xlsx
+++ b/new-info47/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
   <si>
     <t>domain</t>
   </si>
@@ -53,9 +53,6 @@
   </si>
   <si>
     <t>sec.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>pink</t>
   </si>
   <si>
     <t>color</t>
@@ -1368,7 +1365,7 @@
         <v>7</v>
       </c>
       <c r="B3" s="19" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1413,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
@@ -1427,10 +1424,10 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>10</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>11</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1441,10 +1438,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>12</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>13</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1455,10 +1452,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>15</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1469,10 +1466,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" s="14" t="s">
         <v>16</v>
-      </c>
-      <c r="B5" s="14" t="s">
-        <v>17</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1483,10 +1480,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="B6" s="15" t="s">
         <v>18</v>
-      </c>
-      <c r="B6" s="15" t="s">
-        <v>19</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1497,18 +1494,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>20</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="16" t="s">
+        <v>21</v>
+      </c>
+      <c r="G17" s="17" t="s">
         <v>22</v>
-      </c>
-      <c r="G17" s="17" t="s">
-        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1548,49 +1545,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>28</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>29</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="C4" s="8" t="s">
         <v>30</v>
-      </c>
-      <c r="C4" s="8" t="s">
-        <v>31</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>

--- a/new-info47/web.xlsx
+++ b/new-info47/web.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="12600" windowHeight="7635"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="13" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>domain</t>
   </si>
@@ -40,22 +40,22 @@
     <t>color2</t>
   </si>
   <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>necrosia.cloud</t>
+  </si>
+  <si>
+    <t>#ae1c31</t>
+  </si>
+  <si>
+    <t>color</t>
+  </si>
+  <si>
     <t>info</t>
   </si>
   <si>
     <t>json</t>
-  </si>
-  <si>
-    <t>read.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>#ae1c31</t>
-  </si>
-  <si>
-    <t>sec.mousseline.cloud</t>
-  </si>
-  <si>
-    <t>color</t>
   </si>
   <si>
     <t>vernations.cloud</t>
@@ -878,7 +878,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -931,11 +931,15 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1323,13 +1327,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="4"/>
+  <dimension ref="A1:D6"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelRow="5" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.875" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1342,55 +1347,35 @@
       <c r="D1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2" s="18" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="18" t="s">
+      <c r="B2" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="18" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="19" t="s">
-        <v>6</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="20"/>
+      <c r="D2" s="20">
+        <v>46198</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="21"/>
+      <c r="B3" s="19"/>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="22"/>
       <c r="B4" s="13"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:4">
       <c r="A5" s="6"/>
       <c r="B5" s="14"/>
     </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="20"/>
+    <row r="6" spans="1:4">
+      <c r="A6" s="22"/>
       <c r="B6" s="15"/>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="A2" r:id="rId1" display="read.mousseline.cloud"/>
-    <hyperlink ref="A3" r:id="rId1" display="sec.mousseline.cloud"/>
-  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1410,16 +1395,16 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7">

--- a/new-info47/web.xlsx
+++ b/new-info47/web.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="31">
   <si>
     <t>domain</t>
   </si>
@@ -43,16 +43,10 @@
     <t>date</t>
   </si>
   <si>
-    <t>shibor.site</t>
-  </si>
-  <si>
-    <t>#4167b1</t>
-  </si>
-  <si>
-    <t>sec.prefire.site</t>
-  </si>
-  <si>
-    <t>#d62828</t>
+    <t>hypotrachelion.com</t>
+  </si>
+  <si>
+    <t>#8abe98</t>
   </si>
   <si>
     <t>color</t>
@@ -110,9 +104,6 @@
   </si>
   <si>
     <t>#e2e1dd</t>
-  </si>
-  <si>
-    <t>#8abe98</t>
   </si>
   <si>
     <t>droshky.fun</t>
@@ -359,7 +350,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="52">
+  <fills count="51">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -447,12 +438,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF70C588"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4167B1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -797,7 +782,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="21" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -821,16 +806,16 @@
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="24" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -839,89 +824,89 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="44" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="45" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="46" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="47" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="48" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="28" fillId="49" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="51" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="27" fillId="50" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="27">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -974,26 +959,29 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1400,7 +1388,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" ht="16.5" spans="1:4">
+    <row r="2" spans="1:4">
       <c r="A2" s="18" t="s">
         <v>4</v>
       </c>
@@ -1408,36 +1396,33 @@
         <v>5</v>
       </c>
       <c r="D2" s="20">
-        <v>46198</v>
+        <v>46192</v>
       </c>
     </row>
     <row r="3" ht="16.5" spans="1:4">
-      <c r="A3" s="18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="21" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="20">
-        <v>46202</v>
-      </c>
+      <c r="A3" s="21"/>
+      <c r="B3" s="22"/>
+      <c r="D3" s="20"/>
     </row>
     <row r="4" ht="16.5" spans="1:4">
-      <c r="A4" s="18"/>
-      <c r="B4" s="22"/>
+      <c r="A4" s="21"/>
+      <c r="B4" s="23"/>
       <c r="D4" s="20"/>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="18"/>
-      <c r="B5" s="23"/>
+      <c r="A5" s="21"/>
+      <c r="B5" s="24"/>
       <c r="D5" s="20"/>
     </row>
     <row r="6" spans="1:4">
-      <c r="A6" s="24"/>
-      <c r="B6" s="25"/>
+      <c r="A6" s="25"/>
+      <c r="B6" s="26"/>
       <c r="D6" s="20"/>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A2" r:id="rId1" display="hypotrachelion.com" tooltip="https://hypotrachelion.com"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -1457,24 +1442,24 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D2">
         <v>1</v>
@@ -1485,10 +1470,10 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="D3">
         <v>2</v>
@@ -1499,10 +1484,10 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B4" s="13" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D4">
         <v>3</v>
@@ -1513,10 +1498,10 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B5" s="14" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="D5">
         <v>4</v>
@@ -1527,10 +1512,10 @@
     </row>
     <row r="6" spans="1:7">
       <c r="A6" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D6">
         <v>5</v>
@@ -1541,18 +1526,18 @@
     </row>
     <row r="16" spans="1:7">
       <c r="F16" s="16" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17" spans="6:7">
       <c r="F17" s="16" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G17" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1592,49 +1577,49 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>27</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="E3" s="6"/>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="1" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="D4" s="6"/>
       <c r="E4" s="6"/>
     </row>
     <row r="5" spans="1:5">
       <c r="A5" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C5" s="10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D5" s="6"/>
       <c r="E5" s="6"/>
